--- a/街道案件明细表模板.xlsx
+++ b/街道案件明细表模板.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Haidian\海淀区\data\26-6街镇分报告-自动化\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Haidian\Haidian-Report-Producer\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21094" windowHeight="9805"/>
+    <workbookView windowWidth="13551" windowHeight="12291"/>
   </bookViews>
   <sheets>
     <sheet name="案件明细" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>编号</t>
   </si>
@@ -67,22 +67,28 @@
     <t>公园</t>
   </si>
   <si>
-    <t>检查点位 （1级）</t>
-  </si>
-  <si>
-    <t>检查点位 （2级）</t>
-  </si>
-  <si>
-    <t>检查点位 （3级）</t>
-  </si>
-  <si>
-    <t>检查指标 （1级）</t>
-  </si>
-  <si>
-    <t>检查指标 （2级）</t>
-  </si>
-  <si>
-    <t>检查指标 （3级）</t>
+    <t>检查点位
+（1级）</t>
+  </si>
+  <si>
+    <t>检查点位
+（2级）</t>
+  </si>
+  <si>
+    <t>检查点位
+（3级）</t>
+  </si>
+  <si>
+    <t>检查指标
+（1级）</t>
+  </si>
+  <si>
+    <t>检查指标
+（2级）</t>
+  </si>
+  <si>
+    <t>检查指标
+（3级）</t>
   </si>
   <si>
     <t>街镇分中心</t>
@@ -103,10 +109,42 @@
     <t>整改责任单位</t>
   </si>
   <si>
-    <t>处置部门名称 （一级部门）</t>
-  </si>
-  <si>
-    <t>整改时间 （二级部门）</t>
+    <t>处置部门名称
+（一级部门）</t>
+  </si>
+  <si>
+    <t>整改时间
+（二级部门）</t>
+  </si>
+  <si>
+    <t>是否按期整改</t>
+  </si>
+  <si>
+    <t>经纬度</t>
+  </si>
+  <si>
+    <t>商户编号</t>
+  </si>
+  <si>
+    <t>商户名称</t>
+  </si>
+  <si>
+    <t>上报扣分案件</t>
+  </si>
+  <si>
+    <t>解决案件库</t>
+  </si>
+  <si>
+    <t>按期整改</t>
+  </si>
+  <si>
+    <t>超期整改</t>
+  </si>
+  <si>
+    <t>超期未整改(已整改未审核)</t>
+  </si>
+  <si>
+    <t>超期未整改</t>
   </si>
   <si>
     <t>{{ item.编号 }}</t>
@@ -203,6 +241,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -218,13 +263,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -705,19 +743,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -726,7 +764,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -850,23 +888,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1216,183 +1256,202 @@
   <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="6" width="12" customWidth="1"/>
-    <col min="7" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="17" width="18" customWidth="1"/>
-    <col min="18" max="25" width="12" customWidth="1"/>
+    <col min="4" max="4" width="21.5045045045045" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45.45" spans="1:35">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="60.45" spans="1:35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" spans="1:35">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
+      <c r="P2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
